--- a/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 29,18</t>
+          <t>11,71; 28,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 12,89</t>
+          <t>-9,75; 11,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -25,46</t>
+          <t>-45,3; -26,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 20,96</t>
+          <t>2,87; 20,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 14,52</t>
+          <t>-5,21; 14,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,22; -17,2</t>
+          <t>-46,34; -19,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 22,97</t>
+          <t>9,92; 22,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 10,63</t>
+          <t>-3,62; 10,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-43,12; -26,95</t>
+          <t>-43,31; -26,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,45; 47,23</t>
+          <t>15,42; 45,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 20,57</t>
+          <t>-13,3; 17,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,63; -39,32</t>
+          <t>-61,96; -40,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 31,46</t>
+          <t>3,68; 30,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 21,36</t>
+          <t>-6,64; 21,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,39; -23,52</t>
+          <t>-61,72; -28,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,44; 34,26</t>
+          <t>13,31; 33,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 15,58</t>
+          <t>-4,92; 16,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,94; -38,34</t>
+          <t>-58,95; -37,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 27,72</t>
+          <t>13,16; 26,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 12,04</t>
+          <t>-3,89; 11,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,21; -24,1</t>
+          <t>-41,08; -23,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 21,93</t>
+          <t>7,14; 21,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 16,04</t>
+          <t>-0,14; 15,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,28; -20,98</t>
+          <t>-38,48; -21,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 21,98</t>
+          <t>11,85; 21,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 11,43</t>
+          <t>0,79; 11,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-37,73; -25,11</t>
+          <t>-37,1; -25,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 42,59</t>
+          <t>17,1; 40,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 18,48</t>
+          <t>-5,15; 18,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,12; -34,95</t>
+          <t>-55,76; -35,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 32,38</t>
+          <t>9,74; 33,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 23,6</t>
+          <t>-0,26; 22,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,52; -30,57</t>
+          <t>-50,74; -31,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,78; 32,31</t>
+          <t>15,83; 31,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 16,9</t>
+          <t>1,15; 17,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,3; -35,98</t>
+          <t>-50,04; -35,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,12; 33,37</t>
+          <t>16,2; 32,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 16,71</t>
+          <t>-3,09; 15,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-56,26; -36,32</t>
+          <t>-55,75; -36,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,02; 33,85</t>
+          <t>17,83; 33,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 16,03</t>
+          <t>-4,27; 15,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,68; -35,63</t>
+          <t>-54,7; -36,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 31,34</t>
+          <t>19,06; 30,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 13,0</t>
+          <t>-1,41; 12,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-51,76; -38,64</t>
+          <t>-53,0; -39,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,29; 57,2</t>
+          <t>22,79; 56,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 28,53</t>
+          <t>-4,64; 26,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,79; -59,96</t>
+          <t>-80,64; -59,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,78; 58,37</t>
+          <t>24,78; 56,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 26,94</t>
+          <t>-5,79; 26,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,78; -59,87</t>
+          <t>-78,23; -58,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,88; 51,82</t>
+          <t>27,51; 51,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 21,21</t>
+          <t>-2,02; 20,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,29; -62,6</t>
+          <t>-77,4; -63,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,13; 24,55</t>
+          <t>9,96; 24,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 9,81</t>
+          <t>-7,53; 9,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-50,38; -33,13</t>
+          <t>-50,89; -34,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,18; 31,45</t>
+          <t>16,44; 31,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 16,01</t>
+          <t>-2,08; 15,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,48; -26,69</t>
+          <t>-44,46; -26,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,81; 25,64</t>
+          <t>14,59; 25,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 10,08</t>
+          <t>-2,16; 10,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-45,24; -33,48</t>
+          <t>-45,74; -33,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,12; 37,17</t>
+          <t>12,89; 36,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 14,58</t>
+          <t>-10,04; 13,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,6; -48,03</t>
+          <t>-67,71; -50,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,43; 53,71</t>
+          <t>23,47; 52,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 26,88</t>
+          <t>-2,92; 26,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,71; -44,07</t>
+          <t>-64,84; -43,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,54; 39,54</t>
+          <t>20,14; 38,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 15,56</t>
+          <t>-2,97; 15,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,5; -50,46</t>
+          <t>-63,83; -50,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,35; 24,1</t>
+          <t>16,24; 24,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 7,73</t>
+          <t>-0,84; 7,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-44,79; -35,05</t>
+          <t>-45,04; -35,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,76</t>
+          <t>14,95; 22,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,92</t>
+          <t>2,19; 11,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,41; -30,73</t>
+          <t>-40,16; -30,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,89; 22,53</t>
+          <t>16,84; 22,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,52</t>
+          <t>1,9; 8,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -34,21</t>
+          <t>-41,31; -34,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22,77; 36,14</t>
+          <t>22,31; 36,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 11,5</t>
+          <t>-1,2; 11,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -51,59</t>
+          <t>-63,35; -51,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,51; 34,68</t>
+          <t>20,83; 34,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,44; 16,38</t>
+          <t>3,19; 17,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -45,93</t>
+          <t>-56,98; -45,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,7; 33,57</t>
+          <t>23,69; 33,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,57</t>
+          <t>2,69; 11,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,26; -50,45</t>
+          <t>-58,68; -50,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 28,55</t>
+          <t>10,81; 28,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 11,64</t>
+          <t>-9,7; 12,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-45,3; -26,34</t>
+          <t>-46,74; -25,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 20,84</t>
+          <t>3,36; 20,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 14,75</t>
+          <t>-4,67; 14,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,34; -19,96</t>
+          <t>-46,3; -16,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 22,62</t>
+          <t>10,11; 22,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 10,85</t>
+          <t>-2,92; 10,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-43,31; -26,1</t>
+          <t>-43,08; -24,67</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 45,23</t>
+          <t>14,47; 44,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 17,69</t>
+          <t>-13,14; 19,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,96; -40,97</t>
+          <t>-63,42; -39,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 30,66</t>
+          <t>4,54; 30,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 21,72</t>
+          <t>-6,36; 21,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,72; -28,59</t>
+          <t>-61,91; -23,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 33,62</t>
+          <t>13,67; 33,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 16,14</t>
+          <t>-4,04; 16,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; -37,19</t>
+          <t>-58,67; -35,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,16; 26,62</t>
+          <t>12,5; 27,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 11,96</t>
+          <t>-4,15; 12,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -23,69</t>
+          <t>-42,22; -23,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 21,85</t>
+          <t>7,51; 21,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 15,32</t>
+          <t>0,42; 15,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,48; -21,29</t>
+          <t>-37,31; -21,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 21,79</t>
+          <t>11,84; 22,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 11,84</t>
+          <t>0,3; 11,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-37,1; -25,07</t>
+          <t>-37,05; -25,23</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 40,27</t>
+          <t>16,19; 41,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 18,1</t>
+          <t>-5,61; 19,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,76; -35,15</t>
+          <t>-56,94; -34,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 33,1</t>
+          <t>9,95; 32,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 22,95</t>
+          <t>0,52; 22,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,74; -31,99</t>
+          <t>-49,3; -31,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 31,87</t>
+          <t>15,74; 32,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 17,47</t>
+          <t>0,39; 17,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,04; -35,94</t>
+          <t>-50,0; -36,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,2; 32,91</t>
+          <t>16,32; 32,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 15,76</t>
+          <t>-4,08; 15,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-55,75; -36,17</t>
+          <t>-55,74; -35,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,83; 33,63</t>
+          <t>16,39; 33,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 15,83</t>
+          <t>-4,4; 15,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,7; -36,77</t>
+          <t>-55,12; -37,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 30,91</t>
+          <t>19,13; 30,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 12,71</t>
+          <t>-0,22; 13,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-53,0; -39,35</t>
+          <t>-52,32; -39,13</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,79; 56,01</t>
+          <t>23,05; 55,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 26,65</t>
+          <t>-5,87; 25,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,64; -59,26</t>
+          <t>-82,66; -58,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,78; 56,03</t>
+          <t>22,97; 55,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 26,9</t>
+          <t>-6,56; 26,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,23; -58,96</t>
+          <t>-77,85; -61,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,51; 51,41</t>
+          <t>27,31; 50,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 20,43</t>
+          <t>-0,3; 21,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,4; -63,46</t>
+          <t>-77,99; -62,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 24,69</t>
+          <t>10,14; 24,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 9,16</t>
+          <t>-7,1; 9,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-50,89; -34,08</t>
+          <t>-50,59; -33,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,44; 31,22</t>
+          <t>16,08; 31,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 15,83</t>
+          <t>-1,1; 15,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -26,58</t>
+          <t>-43,84; -26,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,59; 25,08</t>
+          <t>14,96; 25,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 10,39</t>
+          <t>-2,37; 10,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -33,44</t>
+          <t>-45,04; -32,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,89; 36,99</t>
+          <t>13,05; 37,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 13,48</t>
+          <t>-9,22; 14,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,71; -50,07</t>
+          <t>-67,11; -49,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,47; 52,62</t>
+          <t>23,25; 53,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 26,52</t>
+          <t>-1,52; 26,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,84; -43,75</t>
+          <t>-64,28; -43,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,14; 38,78</t>
+          <t>20,7; 40,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 15,9</t>
+          <t>-2,94; 16,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,83; -50,41</t>
+          <t>-63,33; -50,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,16</t>
+          <t>16,71; 24,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 7,93</t>
+          <t>-0,83; 8,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-45,04; -35,21</t>
+          <t>-45,23; -35,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,75</t>
+          <t>14,87; 23,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,4</t>
+          <t>2,38; 11,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -30,72</t>
+          <t>-40,55; -31,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,39</t>
+          <t>16,88; 22,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,06</t>
+          <t>1,87; 7,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-41,31; -34,19</t>
+          <t>-41,14; -34,49</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22,31; 36,13</t>
+          <t>23,23; 37,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 11,88</t>
+          <t>-1,16; 12,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,35; -51,8</t>
+          <t>-63,6; -52,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,83; 34,33</t>
+          <t>20,68; 35,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,19; 17,39</t>
+          <t>3,41; 16,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,98; -45,79</t>
+          <t>-57,48; -46,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,69; 33,24</t>
+          <t>23,74; 33,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,69; 11,85</t>
+          <t>2,65; 11,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -50,46</t>
+          <t>-58,81; -50,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-34,26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>20,65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,65</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-35,95</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-35,53</t>
+          <t>-35,99</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-35,67</t>
+          <t>-35,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 28,16</t>
+          <t>3,51; 20,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 12,68</t>
+          <t>-4,15; 14,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,74; -25,57</t>
+          <t>-44,74; -17,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 20,71</t>
+          <t>11,38; 29,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 14,62</t>
+          <t>-9,45; 12,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,3; -16,2</t>
+          <t>-45,96; -25,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 22,14</t>
+          <t>10,32; 22,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 10,86</t>
+          <t>-4,3; 10,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-43,08; -24,67</t>
+          <t>-42,24; -27,12</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-47,05%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>29,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-51,85%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-48,8%</t>
+          <t>-51,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-50,11%</t>
+          <t>-49,42%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 44,61</t>
+          <t>4,81; 31,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 19,19</t>
+          <t>-5,24; 21,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,42; -39,13</t>
+          <t>-59,48; -24,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 30,73</t>
+          <t>15,45; 47,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 21,64</t>
+          <t>-12,84; 20,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,91; -23,78</t>
+          <t>-62,11; -39,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,67; 33,1</t>
+          <t>13,44; 34,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 16,02</t>
+          <t>-5,69; 15,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,67; -35,49</t>
+          <t>-57,9; -39,55</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-28,8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,74</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-33,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,84</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-29,85</t>
+          <t>-34,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-31,18</t>
+          <t>-31,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 27,42</t>
+          <t>6,54; 21,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 12,99</t>
+          <t>0,4; 16,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,22; -23,05</t>
+          <t>-37,3; -19,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 21,59</t>
+          <t>12,69; 27,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 15,47</t>
+          <t>-5,18; 12,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,31; -21,68</t>
+          <t>-43,77; -26,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 22,03</t>
+          <t>11,83; 21,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 11,86</t>
+          <t>-0,09; 11,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-37,05; -25,23</t>
+          <t>-37,37; -25,32</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-39,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>27,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-46,67%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-41,18%</t>
+          <t>-48,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,45%</t>
+          <t>-43,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,19; 41,85</t>
+          <t>8,97; 32,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 19,58</t>
+          <t>0,42; 23,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,94; -34,38</t>
+          <t>-49,51; -28,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 32,69</t>
+          <t>16,59; 42,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 22,26</t>
+          <t>-6,74; 18,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,3; -31,35</t>
+          <t>-58,38; -39,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 32,5</t>
+          <t>15,78; 32,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 17,38</t>
+          <t>-0,11; 16,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,0; -36,2</t>
+          <t>-50,02; -36,63</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>25,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-45,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>24,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>6,19</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-45,27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25,45</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,1</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-45,75</t>
+          <t>-41,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-45,52</t>
+          <t>-43,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 32,52</t>
+          <t>17,02; 33,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 15,12</t>
+          <t>-2,68; 16,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-55,74; -35,74</t>
+          <t>-53,33; -35,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 33,1</t>
+          <t>16,12; 33,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 15,58</t>
+          <t>-2,58; 16,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,12; -37,79</t>
+          <t>-49,97; -31,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,13; 30,97</t>
+          <t>19,37; 31,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 13,44</t>
+          <t>-0,41; 13,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-52,32; -39,13</t>
+          <t>-49,6; -36,61</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38,82%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-68,76%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>38,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-69,92%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-69,79%</t>
+          <t>-63,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-69,86%</t>
+          <t>-66,29%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,05; 55,98</t>
+          <t>24,78; 58,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 25,3</t>
+          <t>-3,72; 26,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,66; -58,47</t>
+          <t>-77,08; -58,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,97; 55,93</t>
+          <t>23,29; 57,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 26,15</t>
+          <t>-3,65; 28,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,85; -61,19</t>
+          <t>-73,26; -53,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,31; 50,6</t>
+          <t>27,88; 51,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 21,66</t>
+          <t>-0,54; 21,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,99; -62,78</t>
+          <t>-72,66; -59,49</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-34,97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>17,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-42,69</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23,75</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,23</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-35,53</t>
+          <t>-41,94</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-39,21</t>
+          <t>-38,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,14; 24,97</t>
+          <t>15,18; 31,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 9,73</t>
+          <t>-1,76; 16,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-50,59; -33,99</t>
+          <t>-43,91; -26,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,08; 31,43</t>
+          <t>10,13; 24,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 15,66</t>
+          <t>-6,97; 9,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,84; -26,55</t>
+          <t>-49,53; -32,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,96; 25,99</t>
+          <t>14,81; 25,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,47</t>
+          <t>-1,91; 10,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-45,04; -32,89</t>
+          <t>-44,6; -32,97</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36,59%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-53,86%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>24,04%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-59,18%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>36,59%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,72%</t>
+          <t>-58,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,13%</t>
+          <t>-56,18%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,05; 37,23</t>
+          <t>21,43; 53,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 14,41</t>
+          <t>-2,54; 26,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,11; -49,67</t>
+          <t>-64,13; -43,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,25; 53,33</t>
+          <t>13,12; 37,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 26,43</t>
+          <t>-9,21; 14,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,28; -43,38</t>
+          <t>-66,06; -47,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,7; 40,33</t>
+          <t>20,54; 39,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 16,4</t>
+          <t>-2,69; 15,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,33; -50,26</t>
+          <t>-62,72; -49,41</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19,08</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,79</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-34,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>20,25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-39,99</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19,08</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,79</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-35,89</t>
+          <t>-38,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-37,82</t>
+          <t>-36,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,71; 24,87</t>
+          <t>14,65; 22,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,19</t>
+          <t>1,75; 10,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-45,23; -35,46</t>
+          <t>-39,27; -29,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,31</t>
+          <t>16,35; 24,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 11,13</t>
+          <t>-1,32; 7,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,55; -31,04</t>
+          <t>-43,16; -34,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,27</t>
+          <t>16,89; 22,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,94</t>
+          <t>1,89; 8,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -34,49</t>
+          <t>-39,89; -33,42</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-50,8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>29,07%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-57,39%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-52,14%</t>
+          <t>-55,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-54,61%</t>
+          <t>-53,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23,23; 37,78</t>
+          <t>20,51; 34,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 12,21</t>
+          <t>2,44; 16,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,6; -52,0</t>
+          <t>-56,01; -44,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,68; 35,26</t>
+          <t>22,77; 36,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,41; 16,93</t>
+          <t>-1,87; 11,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,48; -46,15</t>
+          <t>-60,25; -50,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,12</t>
+          <t>23,7; 33,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,78</t>
+          <t>2,68; 12,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,81; -50,76</t>
+          <t>-56,93; -49,51</t>
         </is>
       </c>
     </row>
